--- a/public/templates/Vendor_sample_template.xlsx
+++ b/public/templates/Vendor_sample_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>Vendor Name</t>
   </si>
@@ -108,12 +108,6 @@
   </si>
   <si>
     <t>GSTIN No.</t>
-  </si>
-  <si>
-    <t>GST Registered Name</t>
-  </si>
-  <si>
-    <t>GSTIN Reg. Date</t>
   </si>
   <si>
     <t>TDS Applicable</t>
@@ -918,13 +912,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1205,7 +1192,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.1416666666667" style="2" customWidth="1"/>
@@ -1222,19 +1209,18 @@
     <col min="19" max="25" width="9.14166666666667" style="2"/>
     <col min="26" max="26" width="11.425" style="2" customWidth="1"/>
     <col min="27" max="27" width="9.14166666666667" style="2"/>
-    <col min="28" max="28" width="15" style="2" customWidth="1"/>
-    <col min="29" max="29" width="11.8583333333333" style="2" customWidth="1"/>
-    <col min="30" max="30" width="11.425" style="2" customWidth="1"/>
-    <col min="31" max="31" width="9.14166666666667" style="2"/>
-    <col min="32" max="32" width="14.1416666666667" style="2" customWidth="1"/>
-    <col min="33" max="36" width="10.8583333333333" style="2" customWidth="1"/>
-    <col min="37" max="37" width="11.1416666666667" style="2" customWidth="1"/>
-    <col min="38" max="38" width="9.14166666666667" style="2"/>
-    <col min="39" max="39" width="13.2833333333333" style="2" customWidth="1"/>
-    <col min="40" max="16384" width="9.14166666666667" style="2"/>
+    <col min="28" max="28" width="11.425" style="2" customWidth="1"/>
+    <col min="29" max="29" width="9.14166666666667" style="2"/>
+    <col min="30" max="30" width="14.1416666666667" style="2" customWidth="1"/>
+    <col min="31" max="34" width="10.8583333333333" style="2" customWidth="1"/>
+    <col min="35" max="35" width="11.1416666666667" style="2" customWidth="1"/>
+    <col min="36" max="36" width="9.14166666666667" style="2"/>
+    <col min="37" max="37" width="13.2833333333333" style="2" customWidth="1"/>
+    <col min="38" max="16383" width="9.14166666666667" style="2"/>
+    <col min="16384" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:39">
+    <row r="1" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:37">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1346,29 +1332,23 @@
       <c r="AK1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="2" ht="99.75" spans="1:39">
+    <row r="2" ht="99.75" spans="1:37">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1380,7 +1360,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1390,41 +1370,39 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
       <c r="AD2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AF2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AK2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL2" s="6"/>
-      <c r="AM2" s="6" t="s">
-        <v>48</v>
-      </c>
     </row>
-    <row r="3" spans="1:39">
+    <row r="3" spans="1:37">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1462,10 +1440,8 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
-      <c r="AL3" s="7"/>
-      <c r="AM3" s="7"/>
     </row>
-    <row r="4" spans="1:39">
+    <row r="4" spans="1:37">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1503,10 +1479,8 @@
       <c r="AI4" s="7"/>
       <c r="AJ4" s="7"/>
       <c r="AK4" s="7"/>
-      <c r="AL4" s="7"/>
-      <c r="AM4" s="7"/>
     </row>
-    <row r="5" spans="1:39">
+    <row r="5" spans="1:37">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1544,10 +1518,8 @@
       <c r="AI5" s="7"/>
       <c r="AJ5" s="7"/>
       <c r="AK5" s="7"/>
-      <c r="AL5" s="7"/>
-      <c r="AM5" s="7"/>
     </row>
-    <row r="6" spans="1:39">
+    <row r="6" spans="1:37">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1585,10 +1557,8 @@
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
       <c r="AK6" s="7"/>
-      <c r="AL6" s="7"/>
-      <c r="AM6" s="7"/>
     </row>
-    <row r="7" spans="1:39">
+    <row r="7" spans="1:37">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1626,10 +1596,8 @@
       <c r="AI7" s="7"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="7"/>
-      <c r="AL7" s="7"/>
-      <c r="AM7" s="7"/>
     </row>
-    <row r="8" spans="1:39">
+    <row r="8" spans="1:37">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1667,10 +1635,8 @@
       <c r="AI8" s="7"/>
       <c r="AJ8" s="7"/>
       <c r="AK8" s="7"/>
-      <c r="AL8" s="7"/>
-      <c r="AM8" s="7"/>
     </row>
-    <row r="9" spans="1:39">
+    <row r="9" spans="1:37">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1708,10 +1674,8 @@
       <c r="AI9" s="7"/>
       <c r="AJ9" s="7"/>
       <c r="AK9" s="7"/>
-      <c r="AL9" s="7"/>
-      <c r="AM9" s="7"/>
     </row>
-    <row r="10" spans="1:39">
+    <row r="10" spans="1:37">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1749,8 +1713,6 @@
       <c r="AI10" s="7"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="7"/>
-      <c r="AL10" s="7"/>
-      <c r="AM10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
